--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260420_203820.xlsx
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
